--- a/docs/Unit Appearance Update.xlsx
+++ b/docs/Unit Appearance Update.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John Thompson\Desktop\REGICIDE PVP\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John Thompson\Desktop\REGICIDE PVP\REGICIDE PVP GAME\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E768C76-84D7-47CC-850E-C02F75EE71E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFF98BA-137E-492B-B3A9-6EA91A1EBFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8BBFC644-6777-4008-94B7-5F16387D8B11}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="108">
   <si>
     <t>Primary Melee Line</t>
   </si>
@@ -179,9 +180,6 @@
     <t>Make his club bigger, currently he is just holding a stick. Unit should be barely clothed with team colored loin cloth and wearing a hat made out of animal hide</t>
   </si>
   <si>
-    <t>Appearance Update</t>
-  </si>
-  <si>
     <t>similar look to club man , but carrying a spear instead</t>
   </si>
   <si>
@@ -240,6 +238,132 @@
   </si>
   <si>
     <t>Dragoon</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Stone</t>
+  </si>
+  <si>
+    <t>Bronze</t>
+  </si>
+  <si>
+    <t>Iron</t>
+  </si>
+  <si>
+    <t>Classical</t>
+  </si>
+  <si>
+    <t>Medieval</t>
+  </si>
+  <si>
+    <t>Enlightenment</t>
+  </si>
+  <si>
+    <t>Headwear</t>
+  </si>
+  <si>
+    <t>Body Garment / Leg / Footwear</t>
+  </si>
+  <si>
+    <t>Stone Age</t>
+  </si>
+  <si>
+    <t>Town Center</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>Barracks</t>
+  </si>
+  <si>
+    <t>Bronze Age</t>
+  </si>
+  <si>
+    <t>Storage Pit</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t>Archery Range</t>
+  </si>
+  <si>
+    <t>Stable</t>
+  </si>
+  <si>
+    <t>Watch Tower</t>
+  </si>
+  <si>
+    <t>Historical Description</t>
+  </si>
+  <si>
+    <t>Iron Age</t>
+  </si>
+  <si>
+    <t>Siege Workshop</t>
+  </si>
+  <si>
+    <t>Blacksmith</t>
+  </si>
+  <si>
+    <t>Wood Walls</t>
+  </si>
+  <si>
+    <t>Wood Gate</t>
+  </si>
+  <si>
+    <t>Classical Age</t>
+  </si>
+  <si>
+    <t>Temple</t>
+  </si>
+  <si>
+    <t>Guard Tower</t>
+  </si>
+  <si>
+    <t>Stone Walls</t>
+  </si>
+  <si>
+    <t>Stone Gate</t>
+  </si>
+  <si>
+    <t>Medieval Age</t>
+  </si>
+  <si>
+    <t>Castle</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Enlightenment Age</t>
+  </si>
+  <si>
+    <t>Fortified Walls (replaces stone walls)</t>
+  </si>
+  <si>
+    <t>Fortified Gate (replaces stone gate)</t>
+  </si>
+  <si>
+    <t>Storehouse (replaces storage pit)</t>
+  </si>
+  <si>
+    <t>Foundry (replaces siege workshop)</t>
+  </si>
+  <si>
+    <t>Arsenal (replaces blacksmith)</t>
+  </si>
+  <si>
+    <t>Bastion (replaces castle)</t>
+  </si>
+  <si>
+    <t>Old Description for Reference / Historical description</t>
+  </si>
+  <si>
+    <t>Signature Props (Items, Weapons, Shields, Accessories, etc.)</t>
   </si>
 </sst>
 </file>
@@ -283,11 +407,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -623,304 +759,1016 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FCAE3AB-5942-4875-A040-071A6CB27E2C}">
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.140625" customWidth="1"/>
-    <col min="2" max="2" width="155.5703125" customWidth="1"/>
+    <col min="1" max="2" width="32.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="29.5703125" customWidth="1"/>
+    <col min="5" max="5" width="57.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="155.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41F166FB-750E-4341-8A90-51BD375B819A}">
+  <dimension ref="A1:B87"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>45</v>
+      <c r="A2" s="4" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
+      <c r="A3" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
+      <c r="A4" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>43</v>
+      <c r="A5" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>44</v>
+      <c r="A7" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
+      <c r="A9" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>47</v>
+      <c r="A10" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>48</v>
+      <c r="A11" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>49</v>
+      <c r="A12" s="4" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>50</v>
+      <c r="A13" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>51</v>
+      <c r="A14" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>64</v>
+      <c r="A15" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>65</v>
+      <c r="A33" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>66</v>
+      <c r="A34" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>24</v>
+      <c r="A36" s="4" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>25</v>
+      <c r="A37" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>26</v>
+      <c r="A39" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>27</v>
+      <c r="A40" s="5" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>28</v>
+      <c r="A41" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>29</v>
+      <c r="A43" s="5" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>30</v>
+      <c r="A44" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>31</v>
+      <c r="A45" s="5" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>32</v>
+      <c r="A46" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>33</v>
+      <c r="A49" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>34</v>
+      <c r="A50" s="4" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>35</v>
+      <c r="A51" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>36</v>
+      <c r="A52" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>37</v>
+      <c r="A53" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>38</v>
+      <c r="A54" s="4" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>39</v>
+      <c r="A55" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
